--- a/output/graficos_regionales/plot_i_ingr_a_2019_biobio.xlsx
+++ b/output/graficos_regionales/plot_i_ingr_a_2019_biobio.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -385,11 +385,6 @@
           <t>valor_previo</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>seleccionado</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -414,9 +409,6 @@
       <c r="F2">
         <v>619746.6899999999</v>
       </c>
-      <c r="G2" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -441,9 +433,6 @@
       <c r="F3">
         <v>636223.25</v>
       </c>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -468,9 +457,6 @@
       <c r="F4">
         <v>641386.0600000001</v>
       </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -495,9 +481,6 @@
       <c r="F5">
         <v>666862.5600000001</v>
       </c>
-      <c r="G5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -522,9 +505,6 @@
       <c r="F6">
         <v>685626.5</v>
       </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -549,9 +529,6 @@
       <c r="F7">
         <v>703647.0600000001</v>
       </c>
-      <c r="G7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -576,9 +553,6 @@
       <c r="F8">
         <v>728532.75</v>
       </c>
-      <c r="G8" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -603,9 +577,6 @@
       <c r="F9">
         <v>738216.4399999999</v>
       </c>
-      <c r="G9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -630,9 +601,6 @@
       <c r="F10">
         <v>752070.5</v>
       </c>
-      <c r="G10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -657,9 +625,6 @@
       <c r="F11">
         <v>769993.3100000001</v>
       </c>
-      <c r="G11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -684,9 +649,6 @@
       <c r="F12">
         <v>803792.5600000001</v>
       </c>
-      <c r="G12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -711,9 +673,6 @@
       <c r="F13">
         <v>856447.88</v>
       </c>
-      <c r="G13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -738,9 +697,6 @@
       <c r="F14">
         <v>857521.62</v>
       </c>
-      <c r="G14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -765,9 +721,6 @@
       <c r="F15">
         <v>898577.12</v>
       </c>
-      <c r="G15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -792,9 +745,6 @@
       <c r="F16">
         <v>910332.5600000001</v>
       </c>
-      <c r="G16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -818,9 +768,6 @@
       </c>
       <c r="F17">
         <v>1022175.75</v>
-      </c>
-      <c r="G17" t="b">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales/plot_i_ingr_a_2019_biobio.xlsx
+++ b/output/graficos_regionales/plot_i_ingr_a_2019_biobio.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,20 +367,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>region_code</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>anio_actual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>valor_actual</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>anio_previo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>valor_previo</t>
         </is>
@@ -398,15 +403,18 @@
         </is>
       </c>
       <c r="C2">
-        <v>2019</v>
+        <v>7</v>
       </c>
       <c r="D2">
+        <v>2019</v>
+      </c>
+      <c r="E2">
         <v>657608.0600000001</v>
       </c>
-      <c r="E2">
-        <v>2018</v>
-      </c>
       <c r="F2">
+        <v>2018</v>
+      </c>
+      <c r="G2">
         <v>619746.6899999999</v>
       </c>
     </row>
@@ -422,15 +430,18 @@
         </is>
       </c>
       <c r="C3">
-        <v>2019</v>
+        <v>16</v>
       </c>
       <c r="D3">
+        <v>2019</v>
+      </c>
+      <c r="E3">
         <v>674451.62</v>
       </c>
-      <c r="E3">
-        <v>2018</v>
-      </c>
       <c r="F3">
+        <v>2018</v>
+      </c>
+      <c r="G3">
         <v>636223.25</v>
       </c>
     </row>
@@ -442,19 +453,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="C4">
-        <v>2019</v>
+        <v>9</v>
       </c>
       <c r="D4">
+        <v>2019</v>
+      </c>
+      <c r="E4">
         <v>682729.5</v>
       </c>
-      <c r="E4">
-        <v>2018</v>
-      </c>
       <c r="F4">
+        <v>2018</v>
+      </c>
+      <c r="G4">
         <v>641386.0600000001</v>
       </c>
     </row>
@@ -470,15 +484,18 @@
         </is>
       </c>
       <c r="C5">
-        <v>2019</v>
+        <v>14</v>
       </c>
       <c r="D5">
+        <v>2019</v>
+      </c>
+      <c r="E5">
         <v>712278</v>
       </c>
-      <c r="E5">
-        <v>2018</v>
-      </c>
       <c r="F5">
+        <v>2018</v>
+      </c>
+      <c r="G5">
         <v>666862.5600000001</v>
       </c>
     </row>
@@ -494,15 +511,18 @@
         </is>
       </c>
       <c r="C6">
-        <v>2019</v>
+        <v>6</v>
       </c>
       <c r="D6">
+        <v>2019</v>
+      </c>
+      <c r="E6">
         <v>722711.9399999999</v>
       </c>
-      <c r="E6">
-        <v>2018</v>
-      </c>
       <c r="F6">
+        <v>2018</v>
+      </c>
+      <c r="G6">
         <v>685626.5</v>
       </c>
     </row>
@@ -518,15 +538,18 @@
         </is>
       </c>
       <c r="C7">
-        <v>2019</v>
+        <v>10</v>
       </c>
       <c r="D7">
+        <v>2019</v>
+      </c>
+      <c r="E7">
         <v>748351.25</v>
       </c>
-      <c r="E7">
-        <v>2018</v>
-      </c>
       <c r="F7">
+        <v>2018</v>
+      </c>
+      <c r="G7">
         <v>703647.0600000001</v>
       </c>
     </row>
@@ -542,15 +565,18 @@
         </is>
       </c>
       <c r="C8">
-        <v>2019</v>
+        <v>8</v>
       </c>
       <c r="D8">
+        <v>2019</v>
+      </c>
+      <c r="E8">
         <v>775852.1899999999</v>
       </c>
-      <c r="E8">
-        <v>2018</v>
-      </c>
       <c r="F8">
+        <v>2018</v>
+      </c>
+      <c r="G8">
         <v>728532.75</v>
       </c>
     </row>
@@ -566,15 +592,18 @@
         </is>
       </c>
       <c r="C9">
-        <v>2019</v>
+        <v>5</v>
       </c>
       <c r="D9">
+        <v>2019</v>
+      </c>
+      <c r="E9">
         <v>780448.9399999999</v>
       </c>
-      <c r="E9">
-        <v>2018</v>
-      </c>
       <c r="F9">
+        <v>2018</v>
+      </c>
+      <c r="G9">
         <v>738216.4399999999</v>
       </c>
     </row>
@@ -586,19 +615,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="C10">
-        <v>2019</v>
+        <v>15</v>
       </c>
       <c r="D10">
+        <v>2019</v>
+      </c>
+      <c r="E10">
         <v>791057</v>
       </c>
-      <c r="E10">
-        <v>2018</v>
-      </c>
       <c r="F10">
+        <v>2018</v>
+      </c>
+      <c r="G10">
         <v>752070.5</v>
       </c>
     </row>
@@ -614,15 +646,18 @@
         </is>
       </c>
       <c r="C11">
-        <v>2019</v>
+        <v>4</v>
       </c>
       <c r="D11">
+        <v>2019</v>
+      </c>
+      <c r="E11">
         <v>814749.8100000001</v>
       </c>
-      <c r="E11">
-        <v>2018</v>
-      </c>
       <c r="F11">
+        <v>2018</v>
+      </c>
+      <c r="G11">
         <v>769993.3100000001</v>
       </c>
     </row>
@@ -638,15 +673,18 @@
         </is>
       </c>
       <c r="C12">
-        <v>2019</v>
+        <v>11</v>
       </c>
       <c r="D12">
+        <v>2019</v>
+      </c>
+      <c r="E12">
         <v>830907.1899999999</v>
       </c>
-      <c r="E12">
-        <v>2018</v>
-      </c>
       <c r="F12">
+        <v>2018</v>
+      </c>
+      <c r="G12">
         <v>803792.5600000001</v>
       </c>
     </row>
@@ -662,15 +700,18 @@
         </is>
       </c>
       <c r="C13">
-        <v>2019</v>
+        <v>1</v>
       </c>
       <c r="D13">
+        <v>2019</v>
+      </c>
+      <c r="E13">
         <v>896717</v>
       </c>
-      <c r="E13">
-        <v>2018</v>
-      </c>
       <c r="F13">
+        <v>2018</v>
+      </c>
+      <c r="G13">
         <v>856447.88</v>
       </c>
     </row>
@@ -682,19 +723,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Magallanes y la Antártica Chilena</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="C14">
-        <v>2019</v>
+        <v>12</v>
       </c>
       <c r="D14">
+        <v>2019</v>
+      </c>
+      <c r="E14">
         <v>899476.25</v>
       </c>
-      <c r="E14">
-        <v>2018</v>
-      </c>
       <c r="F14">
+        <v>2018</v>
+      </c>
+      <c r="G14">
         <v>857521.62</v>
       </c>
     </row>
@@ -710,15 +754,18 @@
         </is>
       </c>
       <c r="C15">
-        <v>2019</v>
+        <v>3</v>
       </c>
       <c r="D15">
+        <v>2019</v>
+      </c>
+      <c r="E15">
         <v>934851.5600000001</v>
       </c>
-      <c r="E15">
-        <v>2018</v>
-      </c>
       <c r="F15">
+        <v>2018</v>
+      </c>
+      <c r="G15">
         <v>898577.12</v>
       </c>
     </row>
@@ -734,15 +781,18 @@
         </is>
       </c>
       <c r="C16">
-        <v>2019</v>
+        <v>13</v>
       </c>
       <c r="D16">
+        <v>2019</v>
+      </c>
+      <c r="E16">
         <v>956815.12</v>
       </c>
-      <c r="E16">
-        <v>2018</v>
-      </c>
       <c r="F16">
+        <v>2018</v>
+      </c>
+      <c r="G16">
         <v>910332.5600000001</v>
       </c>
     </row>
@@ -758,15 +808,18 @@
         </is>
       </c>
       <c r="C17">
-        <v>2019</v>
+        <v>2</v>
       </c>
       <c r="D17">
+        <v>2019</v>
+      </c>
+      <c r="E17">
         <v>1066102.38</v>
       </c>
-      <c r="E17">
-        <v>2018</v>
-      </c>
       <c r="F17">
+        <v>2018</v>
+      </c>
+      <c r="G17">
         <v>1022175.75</v>
       </c>
     </row>

--- a/output/graficos_regionales/plot_i_ingr_a_2019_biobio.xlsx
+++ b/output/graficos_regionales/plot_i_ingr_a_2019_biobio.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="C10">

--- a/output/graficos_regionales/plot_i_ingr_a_2019_biobio.xlsx
+++ b/output/graficos_regionales/plot_i_ingr_a_2019_biobio.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Datos'!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Datos'!$A$1:$G$18</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:45</t>
+    <t xml:space="preserve">2026-08-15 23:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -885,8 +885,27 @@
         <v>1022175.75</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>856472.56</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>812081.12</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/graficos_regionales/plot_i_ingr_a_2019_biobio.xlsx
+++ b/output/graficos_regionales/plot_i_ingr_a_2019_biobio.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-15 23:22</t>
+    <t xml:space="preserve">2026-09-07 11:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
